--- a/서버정보/20261001_리소스배포_운영.xlsx
+++ b/서버정보/20261001_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DD5406-43A2-4CC6-B1AA-DC598BD9DC2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F97CCD-C59B-46A1-AEA5-4160FEE3A5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -6523,7 +6523,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6892,9 +6892,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -28737,7 +28734,7 @@
         <v>317</v>
       </c>
       <c r="Y158" s="95" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="Z158" s="95" t="s">
         <v>965</v>
@@ -28826,7 +28823,7 @@
         <v>317</v>
       </c>
       <c r="Y159" s="95" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="Z159" s="95" t="s">
         <v>1149</v>
@@ -43585,7 +43582,6 @@
       <c r="M138" s="73"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="123"/>
       <c r="B139" s="80" t="s">
         <v>23</v>
       </c>
@@ -43618,7 +43614,6 @@
       <c r="M139" s="74"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A140" s="123"/>
       <c r="B140" s="78" t="s">
         <v>23</v>
       </c>
@@ -53262,6 +53257,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -53405,35 +53415,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -53455,9 +53440,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20261001_리소스배포_운영.xlsx
+++ b/서버정보/20261001_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F97CCD-C59B-46A1-AEA5-4160FEE3A5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B353CF-1BC7-43A1-A518-3E7FE590BBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -5886,10 +5886,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-p-if-brpadb01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5979,6 +5975,10 @@
   </si>
   <si>
     <t>hazr-p-clv-admap-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-if-brpadb02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13542,7 +13542,7 @@
         <v>1133</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" ref="F73:F87" si="34">SUBSTITUTE(E73, "hazr-", "")&amp;"-rule"&amp;O73</f>
@@ -13666,7 +13666,7 @@
         <v>1133</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="34"/>
@@ -13728,7 +13728,7 @@
         <v>1133</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13790,7 +13790,7 @@
         <v>1133</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="34"/>
@@ -27794,7 +27794,7 @@
         <v>1134</v>
       </c>
       <c r="G148" s="74" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H148" s="74" t="s">
         <v>1127</v>
@@ -27815,7 +27815,7 @@
         <v>992</v>
       </c>
       <c r="N148" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O148" s="117" t="str">
         <f t="shared" ref="O148:O157" si="18">SUBSTITUTE(F148,"hazr-","")&amp;"-osdisk"</f>
@@ -27847,7 +27847,7 @@
         <v>345</v>
       </c>
       <c r="Z148" s="95" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AA148" s="95" t="b">
         <v>1</v>
@@ -27883,7 +27883,7 @@
         <v>1135</v>
       </c>
       <c r="G149" s="74" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="H149" s="74" t="s">
         <v>1127</v>
@@ -27904,7 +27904,7 @@
         <v>992</v>
       </c>
       <c r="N149" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O149" s="117" t="str">
         <f t="shared" si="18"/>
@@ -27936,7 +27936,7 @@
         <v>345</v>
       </c>
       <c r="Z149" s="95" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AA149" s="95" t="b">
         <v>1</v>
@@ -27972,7 +27972,7 @@
         <v>1136</v>
       </c>
       <c r="G150" s="74" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H150" s="74" t="s">
         <v>1128</v>
@@ -27993,7 +27993,7 @@
         <v>992</v>
       </c>
       <c r="N150" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O150" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28025,7 +28025,7 @@
         <v>338</v>
       </c>
       <c r="Z150" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA150" s="95" t="b">
         <v>1</v>
@@ -28061,7 +28061,7 @@
         <v>1137</v>
       </c>
       <c r="G151" s="74" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H151" s="74" t="s">
         <v>1128</v>
@@ -28082,7 +28082,7 @@
         <v>992</v>
       </c>
       <c r="N151" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O151" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28114,7 +28114,7 @@
         <v>338</v>
       </c>
       <c r="Z151" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA151" s="95" t="b">
         <v>1</v>
@@ -28150,7 +28150,7 @@
         <v>1138</v>
       </c>
       <c r="G152" s="74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H152" s="74" t="s">
         <v>1128</v>
@@ -28171,7 +28171,7 @@
         <v>992</v>
       </c>
       <c r="N152" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O152" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28203,7 +28203,7 @@
         <v>338</v>
       </c>
       <c r="Z152" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA152" s="95" t="b">
         <v>1</v>
@@ -28239,7 +28239,7 @@
         <v>1139</v>
       </c>
       <c r="G153" s="74" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H153" s="74" t="s">
         <v>1128</v>
@@ -28260,7 +28260,7 @@
         <v>992</v>
       </c>
       <c r="N153" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O153" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28292,7 +28292,7 @@
         <v>338</v>
       </c>
       <c r="Z153" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA153" s="95" t="b">
         <v>1</v>
@@ -28328,7 +28328,7 @@
         <v>1140</v>
       </c>
       <c r="G154" s="74" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="H154" s="74" t="s">
         <v>1129</v>
@@ -28349,7 +28349,7 @@
         <v>992</v>
       </c>
       <c r="N154" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O154" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28381,7 +28381,7 @@
         <v>338</v>
       </c>
       <c r="Z154" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA154" s="95" t="b">
         <v>1</v>
@@ -28417,7 +28417,7 @@
         <v>1141</v>
       </c>
       <c r="G155" s="74" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="H155" s="74" t="s">
         <v>1129</v>
@@ -28438,7 +28438,7 @@
         <v>992</v>
       </c>
       <c r="N155" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O155" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28470,7 +28470,7 @@
         <v>338</v>
       </c>
       <c r="Z155" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA155" s="95" t="b">
         <v>1</v>
@@ -28506,7 +28506,7 @@
         <v>1142</v>
       </c>
       <c r="G156" s="74" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="H156" s="74" t="s">
         <v>1128</v>
@@ -28527,7 +28527,7 @@
         <v>992</v>
       </c>
       <c r="N156" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O156" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28559,7 +28559,7 @@
         <v>338</v>
       </c>
       <c r="Z156" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA156" s="95" t="b">
         <v>1</v>
@@ -28595,7 +28595,7 @@
         <v>1143</v>
       </c>
       <c r="G157" s="95" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="H157" s="95" t="s">
         <v>1128</v>
@@ -28616,7 +28616,7 @@
         <v>992</v>
       </c>
       <c r="N157" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O157" s="120" t="str">
         <f t="shared" si="18"/>
@@ -28648,7 +28648,7 @@
         <v>338</v>
       </c>
       <c r="Z157" s="95" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AA157" s="95" t="b">
         <v>1</v>
@@ -28684,7 +28684,7 @@
         <v>1144</v>
       </c>
       <c r="G158" s="74" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H158" s="74" t="s">
         <v>1022</v>
@@ -28705,7 +28705,7 @@
         <v>992</v>
       </c>
       <c r="N158" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O158" s="117" t="str">
         <f t="shared" ref="O158:O159" si="20">SUBSTITUTE(F158,"hazr-","")&amp;"-osdisk"</f>
@@ -28770,10 +28770,10 @@
         <v>24</v>
       </c>
       <c r="F159" s="74" t="s">
-        <v>1145</v>
+        <v>1168</v>
       </c>
       <c r="G159" s="74" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H159" s="74" t="s">
         <v>998</v>
@@ -28794,11 +28794,11 @@
         <v>992</v>
       </c>
       <c r="N159" s="121" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="O159" s="117" t="str">
         <f t="shared" si="20"/>
-        <v>p-if-brpadb01-osdisk</v>
+        <v>p-if-brpadb02-osdisk</v>
       </c>
       <c r="P159" s="112">
         <v>64</v>
@@ -28811,7 +28811,7 @@
       <c r="T159" s="74"/>
       <c r="U159" s="74" t="str">
         <f t="shared" si="21"/>
-        <v>p-if-brpadb01-nic</v>
+        <v>p-if-brpadb02-nic</v>
       </c>
       <c r="V159" s="95" t="b">
         <v>1</v>
@@ -28826,7 +28826,7 @@
         <v>338</v>
       </c>
       <c r="Z159" s="95" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="AA159" s="95" t="b">
         <v>1</v>
@@ -37965,11 +37965,11 @@
         <v>24</v>
       </c>
       <c r="F168" s="74" t="s">
-        <v>1145</v>
+        <v>1168</v>
       </c>
       <c r="G168" s="74" t="str">
         <f t="shared" si="7"/>
-        <v>p-if-brpadb01-disk01</v>
+        <v>p-if-brpadb02-disk01</v>
       </c>
       <c r="H168" s="74" t="s">
         <v>179</v>
@@ -37979,7 +37979,7 @@
       </c>
       <c r="J168" s="74" t="str">
         <f t="shared" si="8"/>
-        <v>p-if-brpadb01-disk02</v>
+        <v>p-if-brpadb02-disk02</v>
       </c>
       <c r="K168" s="74" t="s">
         <v>179</v>
@@ -43603,7 +43603,7 @@
         <v>233</v>
       </c>
       <c r="H139" s="74" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="I139" s="74"/>
       <c r="J139" s="74"/>
@@ -43635,7 +43635,7 @@
         <v>233</v>
       </c>
       <c r="H140" s="73" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="I140" s="73"/>
       <c r="J140" s="73"/>
@@ -44616,7 +44616,7 @@
         <v>338</v>
       </c>
       <c r="H166" s="114" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="I166" s="82" t="s">
         <v>1134</v>
@@ -44656,7 +44656,7 @@
         <v>338</v>
       </c>
       <c r="H167" s="115" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="I167" s="74" t="s">
         <v>1135</v>
@@ -44696,7 +44696,7 @@
         <v>338</v>
       </c>
       <c r="H168" s="114" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I168" s="82" t="s">
         <v>1136</v>
@@ -44736,7 +44736,7 @@
         <v>338</v>
       </c>
       <c r="H169" s="115" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I169" s="74" t="s">
         <v>1137</v>
@@ -44776,7 +44776,7 @@
         <v>338</v>
       </c>
       <c r="H170" s="114" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I170" s="82" t="s">
         <v>1138</v>
@@ -44816,7 +44816,7 @@
         <v>338</v>
       </c>
       <c r="H171" s="115" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I171" s="74" t="s">
         <v>1139</v>
@@ -44856,7 +44856,7 @@
         <v>338</v>
       </c>
       <c r="H172" s="114" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I172" s="82" t="s">
         <v>1140</v>
@@ -44896,7 +44896,7 @@
         <v>338</v>
       </c>
       <c r="H173" s="115" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I173" s="74" t="s">
         <v>1141</v>
@@ -44936,7 +44936,7 @@
         <v>338</v>
       </c>
       <c r="H174" s="114" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I174" s="82" t="s">
         <v>1142</v>
@@ -44976,7 +44976,7 @@
         <v>338</v>
       </c>
       <c r="H175" s="115" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="I175" s="115" t="s">
         <v>1143</v>
@@ -45045,7 +45045,7 @@
       </c>
       <c r="E177" s="115" t="str">
         <f t="shared" si="7"/>
-        <v>p-if-brpadb01-nsg</v>
+        <v>p-if-brpadb02-nsg</v>
       </c>
       <c r="F177" s="115" t="s">
         <v>317</v>
@@ -45054,17 +45054,17 @@
         <v>338</v>
       </c>
       <c r="H177" s="115" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="I177" s="74" t="s">
-        <v>1145</v>
+        <v>1168</v>
       </c>
       <c r="J177" s="115" t="s">
         <v>922</v>
       </c>
       <c r="K177" s="115" t="str">
         <f t="shared" si="11"/>
-        <v>p-if-brpadb01-nic</v>
+        <v>p-if-brpadb02-nic</v>
       </c>
       <c r="L177" s="115" t="s">
         <v>226</v>
@@ -50047,7 +50047,7 @@
         <v>24</v>
       </c>
       <c r="F46" s="82" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G46" s="82" t="s">
         <v>111</v>
@@ -50072,7 +50072,7 @@
         <v>1119</v>
       </c>
       <c r="N46" s="82" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="O46" s="82" t="s">
         <v>108</v>
@@ -50100,7 +50100,7 @@
         <v>24</v>
       </c>
       <c r="F47" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G47" s="74" t="s">
         <v>111</v>
@@ -50125,7 +50125,7 @@
         <v>1120</v>
       </c>
       <c r="N47" s="74" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="O47" s="74" t="s">
         <v>108</v>
@@ -50153,7 +50153,7 @@
         <v>24</v>
       </c>
       <c r="F48" s="82" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G48" s="82" t="s">
         <v>111</v>
@@ -50178,7 +50178,7 @@
         <v>1120</v>
       </c>
       <c r="N48" s="82" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="O48" s="82" t="s">
         <v>108</v>
@@ -50206,7 +50206,7 @@
         <v>24</v>
       </c>
       <c r="F49" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G49" s="74" t="s">
         <v>111</v>
@@ -50231,7 +50231,7 @@
         <v>1120</v>
       </c>
       <c r="N49" s="74" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="O49" s="74" t="s">
         <v>108</v>
@@ -50259,7 +50259,7 @@
         <v>24</v>
       </c>
       <c r="F50" s="82" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G50" s="82" t="s">
         <v>111</v>
@@ -50284,7 +50284,7 @@
         <v>1120</v>
       </c>
       <c r="N50" s="82" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="O50" s="82" t="s">
         <v>108</v>
@@ -52786,7 +52786,7 @@
         <v>1133</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" si="15"/>
@@ -52852,7 +52852,7 @@
         <v>1133</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="15"/>
@@ -52885,7 +52885,7 @@
         <v>1133</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="15"/>
@@ -52918,7 +52918,7 @@
         <v>1133</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="15"/>
@@ -53257,21 +53257,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -53415,10 +53400,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -53440,19 +53450,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20261001_리소스배포_운영.xlsx
+++ b/서버정보/20261001_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B353CF-1BC7-43A1-A518-3E7FE590BBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE34A540-0409-4803-B1A0-5AF4C7F5B593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8156" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8154" uniqueCount="1167">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5791,26 +5791,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.158.128.20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.158.144.50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.158.144.70</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.158.144.130</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.158.144.140</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1,2,3</t>
   </si>
   <si>
@@ -5830,14 +5810,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.158.144.150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10.158.128.50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-p-clv-rg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5978,7 +5950,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-p-if-brpadb02</t>
+    <t>hazr-p-if-brpadb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.133.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.159.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.159.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.159.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.158.159.40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13539,10 +13531,10 @@
         <v>CLV</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" ref="F73:F87" si="34">SUBSTITUTE(E73, "hazr-", "")&amp;"-rule"&amp;O73</f>
@@ -13601,7 +13593,7 @@
         <v>CLV</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E74" s="74" t="s">
         <v>1117</v>
@@ -13663,10 +13655,10 @@
         <v>CLV</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="34"/>
@@ -13725,10 +13717,10 @@
         <v>CLV</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13787,10 +13779,10 @@
         <v>CLV</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="34"/>
@@ -27785,19 +27777,19 @@
         <v>CLV</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E148" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="82" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="G148" s="74" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="H148" s="74" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="I148" s="74">
         <v>4</v>
@@ -27815,7 +27807,7 @@
         <v>992</v>
       </c>
       <c r="N148" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O148" s="117" t="str">
         <f t="shared" ref="O148:O157" si="18">SUBSTITUTE(F148,"hazr-","")&amp;"-osdisk"</f>
@@ -27847,7 +27839,7 @@
         <v>345</v>
       </c>
       <c r="Z148" s="95" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="AA148" s="95" t="b">
         <v>1</v>
@@ -27874,19 +27866,19 @@
         <v>CLV</v>
       </c>
       <c r="D149" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E149" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F149" s="74" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="G149" s="74" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="H149" s="74" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="I149" s="74">
         <v>4</v>
@@ -27904,7 +27896,7 @@
         <v>992</v>
       </c>
       <c r="N149" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O149" s="117" t="str">
         <f t="shared" si="18"/>
@@ -27936,7 +27928,7 @@
         <v>345</v>
       </c>
       <c r="Z149" s="95" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="AA149" s="95" t="b">
         <v>1</v>
@@ -27963,19 +27955,19 @@
         <v>CLV</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E150" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F150" s="82" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="G150" s="74" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="H150" s="74" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I150" s="74">
         <v>4</v>
@@ -27993,7 +27985,7 @@
         <v>992</v>
       </c>
       <c r="N150" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O150" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28025,7 +28017,7 @@
         <v>338</v>
       </c>
       <c r="Z150" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA150" s="95" t="b">
         <v>1</v>
@@ -28052,19 +28044,19 @@
         <v>CLV</v>
       </c>
       <c r="D151" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E151" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F151" s="74" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="G151" s="74" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="H151" s="74" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I151" s="74">
         <v>4</v>
@@ -28082,7 +28074,7 @@
         <v>992</v>
       </c>
       <c r="N151" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O151" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28114,7 +28106,7 @@
         <v>338</v>
       </c>
       <c r="Z151" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA151" s="95" t="b">
         <v>1</v>
@@ -28141,19 +28133,19 @@
         <v>CLV</v>
       </c>
       <c r="D152" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E152" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="82" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G152" s="74" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="H152" s="74" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I152" s="74">
         <v>4</v>
@@ -28171,7 +28163,7 @@
         <v>992</v>
       </c>
       <c r="N152" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O152" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28203,7 +28195,7 @@
         <v>338</v>
       </c>
       <c r="Z152" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA152" s="95" t="b">
         <v>1</v>
@@ -28230,19 +28222,19 @@
         <v>CLV</v>
       </c>
       <c r="D153" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E153" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F153" s="74" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G153" s="74" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="H153" s="74" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I153" s="74">
         <v>4</v>
@@ -28260,7 +28252,7 @@
         <v>992</v>
       </c>
       <c r="N153" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O153" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28292,7 +28284,7 @@
         <v>338</v>
       </c>
       <c r="Z153" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA153" s="95" t="b">
         <v>1</v>
@@ -28319,19 +28311,19 @@
         <v>CLV</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E154" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F154" s="82" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G154" s="74" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="H154" s="74" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="I154" s="74">
         <v>2</v>
@@ -28349,7 +28341,7 @@
         <v>992</v>
       </c>
       <c r="N154" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O154" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28381,7 +28373,7 @@
         <v>338</v>
       </c>
       <c r="Z154" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA154" s="95" t="b">
         <v>1</v>
@@ -28408,19 +28400,19 @@
         <v>CLV</v>
       </c>
       <c r="D155" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E155" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F155" s="74" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G155" s="74" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
       <c r="H155" s="74" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="I155" s="74">
         <v>2</v>
@@ -28438,7 +28430,7 @@
         <v>992</v>
       </c>
       <c r="N155" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O155" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28470,7 +28462,7 @@
         <v>338</v>
       </c>
       <c r="Z155" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA155" s="95" t="b">
         <v>1</v>
@@ -28497,19 +28489,19 @@
         <v>CLV</v>
       </c>
       <c r="D156" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E156" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F156" s="82" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="G156" s="74" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="H156" s="74" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I156" s="74">
         <v>4</v>
@@ -28527,7 +28519,7 @@
         <v>992</v>
       </c>
       <c r="N156" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O156" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28559,7 +28551,7 @@
         <v>338</v>
       </c>
       <c r="Z156" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA156" s="95" t="b">
         <v>1</v>
@@ -28586,19 +28578,19 @@
         <v>CLV</v>
       </c>
       <c r="D157" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E157" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="95" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="G157" s="95" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
       <c r="H157" s="95" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="I157" s="95">
         <v>4</v>
@@ -28616,7 +28608,7 @@
         <v>992</v>
       </c>
       <c r="N157" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O157" s="120" t="str">
         <f t="shared" si="18"/>
@@ -28648,7 +28640,7 @@
         <v>338</v>
       </c>
       <c r="Z157" s="95" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="AA157" s="95" t="b">
         <v>1</v>
@@ -28681,10 +28673,10 @@
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="G158" s="74" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="H158" s="74" t="s">
         <v>1022</v>
@@ -28705,7 +28697,7 @@
         <v>992</v>
       </c>
       <c r="N158" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O158" s="117" t="str">
         <f t="shared" ref="O158:O159" si="20">SUBSTITUTE(F158,"hazr-","")&amp;"-osdisk"</f>
@@ -28770,10 +28762,10 @@
         <v>24</v>
       </c>
       <c r="F159" s="74" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="G159" s="74" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="H159" s="74" t="s">
         <v>998</v>
@@ -28794,11 +28786,11 @@
         <v>992</v>
       </c>
       <c r="N159" s="121" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="O159" s="117" t="str">
         <f t="shared" si="20"/>
-        <v>p-if-brpadb02-osdisk</v>
+        <v>p-if-brpadb01-osdisk</v>
       </c>
       <c r="P159" s="112">
         <v>64</v>
@@ -28811,7 +28803,7 @@
       <c r="T159" s="74"/>
       <c r="U159" s="74" t="str">
         <f t="shared" si="21"/>
-        <v>p-if-brpadb02-nic</v>
+        <v>p-if-brpadb01-nic</v>
       </c>
       <c r="V159" s="95" t="b">
         <v>1</v>
@@ -28826,7 +28818,7 @@
         <v>338</v>
       </c>
       <c r="Z159" s="95" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="AA159" s="95" t="b">
         <v>1</v>
@@ -37354,13 +37346,13 @@
         <v>CLV</v>
       </c>
       <c r="D157" s="78" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E157" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="82" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="G157" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37409,13 +37401,13 @@
         <v>CLV</v>
       </c>
       <c r="D158" s="80" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E158" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="G158" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37464,13 +37456,13 @@
         <v>CLV</v>
       </c>
       <c r="D159" s="78" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E159" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F159" s="82" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="G159" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37519,13 +37511,13 @@
         <v>CLV</v>
       </c>
       <c r="D160" s="80" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E160" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F160" s="74" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="G160" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37574,13 +37566,13 @@
         <v>CLV</v>
       </c>
       <c r="D161" s="78" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E161" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F161" s="82" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G161" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37629,13 +37621,13 @@
         <v>CLV</v>
       </c>
       <c r="D162" s="80" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E162" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F162" s="74" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G162" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37684,13 +37676,13 @@
         <v>CLV</v>
       </c>
       <c r="D163" s="78" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E163" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F163" s="82" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G163" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37739,13 +37731,13 @@
         <v>CLV</v>
       </c>
       <c r="D164" s="80" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E164" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F164" s="74" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G164" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37794,13 +37786,13 @@
         <v>CLV</v>
       </c>
       <c r="D165" s="78" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E165" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F165" s="82" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="G165" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37849,13 +37841,13 @@
         <v>CLV</v>
       </c>
       <c r="D166" s="80" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E166" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F166" s="115" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="G166" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37910,7 +37902,7 @@
         <v>24</v>
       </c>
       <c r="F167" s="73" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="G167" s="73" t="str">
         <f t="shared" ref="G167:G170" si="7">SUBSTITUTE(F167,"hazr-","")&amp;"-disk01"</f>
@@ -37965,11 +37957,11 @@
         <v>24</v>
       </c>
       <c r="F168" s="74" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="G168" s="74" t="str">
         <f t="shared" si="7"/>
-        <v>p-if-brpadb02-disk01</v>
+        <v>p-if-brpadb01-disk01</v>
       </c>
       <c r="H168" s="74" t="s">
         <v>179</v>
@@ -37979,7 +37971,7 @@
       </c>
       <c r="J168" s="74" t="str">
         <f t="shared" si="8"/>
-        <v>p-if-brpadb02-disk02</v>
+        <v>p-if-brpadb01-disk02</v>
       </c>
       <c r="K168" s="74" t="s">
         <v>179</v>
@@ -43603,7 +43595,7 @@
         <v>233</v>
       </c>
       <c r="H139" s="74" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="I139" s="74"/>
       <c r="J139" s="74"/>
@@ -43635,7 +43627,7 @@
         <v>233</v>
       </c>
       <c r="H140" s="73" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
       <c r="I140" s="73"/>
       <c r="J140" s="73"/>
@@ -44616,10 +44608,10 @@
         <v>338</v>
       </c>
       <c r="H166" s="114" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="I166" s="82" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="J166" s="114" t="s">
         <v>922</v>
@@ -44656,10 +44648,10 @@
         <v>338</v>
       </c>
       <c r="H167" s="115" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="I167" s="74" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="J167" s="115" t="s">
         <v>922</v>
@@ -44696,10 +44688,10 @@
         <v>338</v>
       </c>
       <c r="H168" s="114" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I168" s="82" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="J168" s="114" t="s">
         <v>922</v>
@@ -44736,10 +44728,10 @@
         <v>338</v>
       </c>
       <c r="H169" s="115" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I169" s="74" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="J169" s="115" t="s">
         <v>922</v>
@@ -44776,10 +44768,10 @@
         <v>338</v>
       </c>
       <c r="H170" s="114" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I170" s="82" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="J170" s="114" t="s">
         <v>922</v>
@@ -44816,10 +44808,10 @@
         <v>338</v>
       </c>
       <c r="H171" s="115" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I171" s="74" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="J171" s="115" t="s">
         <v>922</v>
@@ -44856,10 +44848,10 @@
         <v>338</v>
       </c>
       <c r="H172" s="114" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I172" s="82" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="J172" s="114" t="s">
         <v>922</v>
@@ -44896,10 +44888,10 @@
         <v>338</v>
       </c>
       <c r="H173" s="115" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I173" s="74" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="J173" s="115" t="s">
         <v>922</v>
@@ -44936,10 +44928,10 @@
         <v>338</v>
       </c>
       <c r="H174" s="114" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I174" s="82" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="J174" s="114" t="s">
         <v>922</v>
@@ -44976,10 +44968,10 @@
         <v>338</v>
       </c>
       <c r="H175" s="115" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="I175" s="115" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="J175" s="115" t="s">
         <v>922</v>
@@ -45018,7 +45010,7 @@
         <v>965</v>
       </c>
       <c r="I176" s="73" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="J176" s="114" t="s">
         <v>922</v>
@@ -45045,7 +45037,7 @@
       </c>
       <c r="E177" s="115" t="str">
         <f t="shared" si="7"/>
-        <v>p-if-brpadb02-nsg</v>
+        <v>p-if-brpadb01-nsg</v>
       </c>
       <c r="F177" s="115" t="s">
         <v>317</v>
@@ -45054,17 +45046,17 @@
         <v>338</v>
       </c>
       <c r="H177" s="115" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="I177" s="74" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
       <c r="J177" s="115" t="s">
         <v>922</v>
       </c>
       <c r="K177" s="115" t="str">
         <f t="shared" si="11"/>
-        <v>p-if-brpadb02-nic</v>
+        <v>p-if-brpadb01-nic</v>
       </c>
       <c r="L177" s="115" t="s">
         <v>226</v>
@@ -50047,7 +50039,7 @@
         <v>24</v>
       </c>
       <c r="F46" s="82" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="G46" s="82" t="s">
         <v>111</v>
@@ -50056,7 +50048,7 @@
         <v>1016</v>
       </c>
       <c r="I46" s="82" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J46" s="82" t="s">
         <v>102</v>
@@ -50072,13 +50064,13 @@
         <v>1119</v>
       </c>
       <c r="N46" s="82" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="O46" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P46" s="82" t="s">
-        <v>1121</v>
+        <v>1162</v>
       </c>
       <c r="Q46" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50100,7 +50092,7 @@
         <v>24</v>
       </c>
       <c r="F47" s="74" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
       <c r="G47" s="74" t="s">
         <v>111</v>
@@ -50109,7 +50101,7 @@
         <v>1016</v>
       </c>
       <c r="I47" s="74" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J47" s="74" t="s">
         <v>102</v>
@@ -50125,13 +50117,13 @@
         <v>1120</v>
       </c>
       <c r="N47" s="74" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="O47" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P47" s="74" t="s">
-        <v>1122</v>
+        <v>1163</v>
       </c>
       <c r="Q47" s="74" t="str">
         <f t="shared" si="6"/>
@@ -50153,7 +50145,7 @@
         <v>24</v>
       </c>
       <c r="F48" s="82" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="G48" s="82" t="s">
         <v>111</v>
@@ -50162,7 +50154,7 @@
         <v>1016</v>
       </c>
       <c r="I48" s="82" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J48" s="82" t="s">
         <v>102</v>
@@ -50178,13 +50170,13 @@
         <v>1120</v>
       </c>
       <c r="N48" s="82" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="O48" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P48" s="82" t="s">
-        <v>1123</v>
+        <v>1164</v>
       </c>
       <c r="Q48" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50206,7 +50198,7 @@
         <v>24</v>
       </c>
       <c r="F49" s="74" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="G49" s="74" t="s">
         <v>111</v>
@@ -50215,7 +50207,7 @@
         <v>1016</v>
       </c>
       <c r="I49" s="74" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J49" s="74" t="s">
         <v>102</v>
@@ -50231,13 +50223,13 @@
         <v>1120</v>
       </c>
       <c r="N49" s="74" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="O49" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P49" s="74" t="s">
-        <v>1124</v>
+        <v>1165</v>
       </c>
       <c r="Q49" s="74" t="str">
         <f t="shared" si="6"/>
@@ -50259,7 +50251,7 @@
         <v>24</v>
       </c>
       <c r="F50" s="82" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="G50" s="82" t="s">
         <v>111</v>
@@ -50268,7 +50260,7 @@
         <v>1016</v>
       </c>
       <c r="I50" s="82" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J50" s="82" t="s">
         <v>102</v>
@@ -50284,13 +50276,13 @@
         <v>1120</v>
       </c>
       <c r="N50" s="82" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="O50" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P50" s="82" t="s">
-        <v>1125</v>
+        <v>1166</v>
       </c>
       <c r="Q50" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50317,7 +50309,7 @@
         <v>1016</v>
       </c>
       <c r="I51" s="74" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J51" s="74" t="s">
         <v>102</v>
@@ -50336,9 +50328,7 @@
       <c r="O51" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="P51" s="74" t="s">
-        <v>1132</v>
-      </c>
+      <c r="P51" s="74"/>
       <c r="Q51" s="74" t="str">
         <f t="shared" si="6"/>
         <v>-bp</v>
@@ -50364,7 +50354,7 @@
         <v>1016</v>
       </c>
       <c r="I52" s="82" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="J52" s="82" t="s">
         <v>102</v>
@@ -50383,9 +50373,7 @@
       <c r="O52" s="82" t="s">
         <v>108</v>
       </c>
-      <c r="P52" s="82" t="s">
-        <v>1131</v>
-      </c>
+      <c r="P52" s="82"/>
       <c r="Q52" s="82" t="str">
         <f t="shared" si="6"/>
         <v>-bp</v>
@@ -52783,17 +52771,17 @@
         <v>CLV</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-web-lb-pb443</v>
       </c>
       <c r="G73" s="82" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="H73" s="82">
         <v>443</v>
@@ -52816,7 +52804,7 @@
         <v>CLV</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E74" s="74" t="s">
         <v>1117</v>
@@ -52826,7 +52814,7 @@
         <v>p-dis-clvap-lb-pb8080</v>
       </c>
       <c r="G74" s="74" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="H74" s="74">
         <v>8080</v>
@@ -52849,17 +52837,17 @@
         <v>CLV</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-ssrap-lb-pb8080</v>
       </c>
       <c r="G75" s="82" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="H75" s="82">
         <v>8080</v>
@@ -52882,17 +52870,17 @@
         <v>CLV</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-admweb-lb-pb443</v>
       </c>
       <c r="G76" s="74" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="H76" s="74">
         <v>443</v>
@@ -52915,17 +52903,17 @@
         <v>CLV</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-admap-lb-pb8080</v>
       </c>
       <c r="G77" s="82" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="H77" s="82">
         <v>8080</v>

--- a/서버정보/20261001_리소스배포_운영.xlsx
+++ b/서버정보/20261001_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE34A540-0409-4803-B1A0-5AF4C7F5B593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF02489-BB04-4A3B-BFEE-D81C565C7694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8154" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8154" uniqueCount="1166">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5768,10 +5768,6 @@
   </si>
   <si>
     <t>PRD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-p-dis-rg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -13531,10 +13527,10 @@
         <v>CLV</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" ref="F73:F87" si="34">SUBSTITUTE(E73, "hazr-", "")&amp;"-rule"&amp;O73</f>
@@ -13593,10 +13589,10 @@
         <v>CLV</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13655,10 +13651,10 @@
         <v>CLV</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="34"/>
@@ -13717,10 +13713,10 @@
         <v>CLV</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13779,10 +13775,10 @@
         <v>CLV</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="34"/>
@@ -27777,19 +27773,19 @@
         <v>CLV</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E148" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="82" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G148" s="74" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H148" s="74" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="I148" s="74">
         <v>4</v>
@@ -27807,7 +27803,7 @@
         <v>992</v>
       </c>
       <c r="N148" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O148" s="117" t="str">
         <f t="shared" ref="O148:O157" si="18">SUBSTITUTE(F148,"hazr-","")&amp;"-osdisk"</f>
@@ -27839,7 +27835,7 @@
         <v>345</v>
       </c>
       <c r="Z148" s="95" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AA148" s="95" t="b">
         <v>1</v>
@@ -27866,19 +27862,19 @@
         <v>CLV</v>
       </c>
       <c r="D149" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E149" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F149" s="74" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G149" s="74" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H149" s="74" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="I149" s="74">
         <v>4</v>
@@ -27896,7 +27892,7 @@
         <v>992</v>
       </c>
       <c r="N149" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O149" s="117" t="str">
         <f t="shared" si="18"/>
@@ -27928,7 +27924,7 @@
         <v>345</v>
       </c>
       <c r="Z149" s="95" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="AA149" s="95" t="b">
         <v>1</v>
@@ -27955,19 +27951,19 @@
         <v>CLV</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E150" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F150" s="82" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G150" s="74" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H150" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I150" s="74">
         <v>4</v>
@@ -27985,7 +27981,7 @@
         <v>992</v>
       </c>
       <c r="N150" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O150" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28017,7 +28013,7 @@
         <v>338</v>
       </c>
       <c r="Z150" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA150" s="95" t="b">
         <v>1</v>
@@ -28044,19 +28040,19 @@
         <v>CLV</v>
       </c>
       <c r="D151" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E151" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F151" s="74" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G151" s="74" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H151" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I151" s="74">
         <v>4</v>
@@ -28074,7 +28070,7 @@
         <v>992</v>
       </c>
       <c r="N151" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O151" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28106,7 +28102,7 @@
         <v>338</v>
       </c>
       <c r="Z151" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA151" s="95" t="b">
         <v>1</v>
@@ -28133,19 +28129,19 @@
         <v>CLV</v>
       </c>
       <c r="D152" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E152" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="82" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G152" s="74" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H152" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I152" s="74">
         <v>4</v>
@@ -28163,7 +28159,7 @@
         <v>992</v>
       </c>
       <c r="N152" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O152" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28195,7 +28191,7 @@
         <v>338</v>
       </c>
       <c r="Z152" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA152" s="95" t="b">
         <v>1</v>
@@ -28222,19 +28218,19 @@
         <v>CLV</v>
       </c>
       <c r="D153" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E153" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F153" s="74" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G153" s="74" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H153" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I153" s="74">
         <v>4</v>
@@ -28252,7 +28248,7 @@
         <v>992</v>
       </c>
       <c r="N153" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O153" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28284,7 +28280,7 @@
         <v>338</v>
       </c>
       <c r="Z153" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA153" s="95" t="b">
         <v>1</v>
@@ -28311,19 +28307,19 @@
         <v>CLV</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E154" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F154" s="82" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G154" s="74" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H154" s="74" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="I154" s="74">
         <v>2</v>
@@ -28341,7 +28337,7 @@
         <v>992</v>
       </c>
       <c r="N154" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O154" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28373,7 +28369,7 @@
         <v>338</v>
       </c>
       <c r="Z154" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA154" s="95" t="b">
         <v>1</v>
@@ -28400,19 +28396,19 @@
         <v>CLV</v>
       </c>
       <c r="D155" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E155" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F155" s="74" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G155" s="74" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H155" s="74" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="I155" s="74">
         <v>2</v>
@@ -28430,7 +28426,7 @@
         <v>992</v>
       </c>
       <c r="N155" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O155" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28462,7 +28458,7 @@
         <v>338</v>
       </c>
       <c r="Z155" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA155" s="95" t="b">
         <v>1</v>
@@ -28489,19 +28485,19 @@
         <v>CLV</v>
       </c>
       <c r="D156" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E156" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F156" s="82" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G156" s="74" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H156" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I156" s="74">
         <v>4</v>
@@ -28519,7 +28515,7 @@
         <v>992</v>
       </c>
       <c r="N156" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O156" s="117" t="str">
         <f t="shared" si="18"/>
@@ -28551,7 +28547,7 @@
         <v>338</v>
       </c>
       <c r="Z156" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA156" s="95" t="b">
         <v>1</v>
@@ -28578,19 +28574,19 @@
         <v>CLV</v>
       </c>
       <c r="D157" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E157" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="95" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G157" s="95" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H157" s="95" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="I157" s="95">
         <v>4</v>
@@ -28608,7 +28604,7 @@
         <v>992</v>
       </c>
       <c r="N157" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O157" s="120" t="str">
         <f t="shared" si="18"/>
@@ -28640,7 +28636,7 @@
         <v>338</v>
       </c>
       <c r="Z157" s="95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AA157" s="95" t="b">
         <v>1</v>
@@ -28673,10 +28669,10 @@
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G158" s="74" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="H158" s="74" t="s">
         <v>1022</v>
@@ -28697,7 +28693,7 @@
         <v>992</v>
       </c>
       <c r="N158" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O158" s="117" t="str">
         <f t="shared" ref="O158:O159" si="20">SUBSTITUTE(F158,"hazr-","")&amp;"-osdisk"</f>
@@ -28762,10 +28758,10 @@
         <v>24</v>
       </c>
       <c r="F159" s="74" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G159" s="74" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H159" s="74" t="s">
         <v>998</v>
@@ -28786,7 +28782,7 @@
         <v>992</v>
       </c>
       <c r="N159" s="121" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="O159" s="117" t="str">
         <f t="shared" si="20"/>
@@ -28818,7 +28814,7 @@
         <v>338</v>
       </c>
       <c r="Z159" s="95" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="AA159" s="95" t="b">
         <v>1</v>
@@ -37346,13 +37342,13 @@
         <v>CLV</v>
       </c>
       <c r="D157" s="78" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E157" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="82" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G157" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37401,13 +37397,13 @@
         <v>CLV</v>
       </c>
       <c r="D158" s="80" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E158" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G158" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37456,13 +37452,13 @@
         <v>CLV</v>
       </c>
       <c r="D159" s="78" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E159" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F159" s="82" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G159" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37511,13 +37507,13 @@
         <v>CLV</v>
       </c>
       <c r="D160" s="80" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E160" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F160" s="74" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G160" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37566,13 +37562,13 @@
         <v>CLV</v>
       </c>
       <c r="D161" s="78" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E161" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F161" s="82" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G161" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37621,13 +37617,13 @@
         <v>CLV</v>
       </c>
       <c r="D162" s="80" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E162" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F162" s="74" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G162" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37676,13 +37672,13 @@
         <v>CLV</v>
       </c>
       <c r="D163" s="78" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E163" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F163" s="82" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G163" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37731,13 +37727,13 @@
         <v>CLV</v>
       </c>
       <c r="D164" s="80" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E164" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F164" s="74" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G164" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37786,13 +37782,13 @@
         <v>CLV</v>
       </c>
       <c r="D165" s="78" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E165" s="78" t="s">
         <v>24</v>
       </c>
       <c r="F165" s="82" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G165" s="73" t="str">
         <f t="shared" si="4"/>
@@ -37841,13 +37837,13 @@
         <v>CLV</v>
       </c>
       <c r="D166" s="80" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E166" s="80" t="s">
         <v>24</v>
       </c>
       <c r="F166" s="115" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G166" s="74" t="str">
         <f t="shared" si="4"/>
@@ -37902,7 +37898,7 @@
         <v>24</v>
       </c>
       <c r="F167" s="73" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G167" s="73" t="str">
         <f t="shared" ref="G167:G170" si="7">SUBSTITUTE(F167,"hazr-","")&amp;"-disk01"</f>
@@ -37957,7 +37953,7 @@
         <v>24</v>
       </c>
       <c r="F168" s="74" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G168" s="74" t="str">
         <f t="shared" si="7"/>
@@ -43595,7 +43591,7 @@
         <v>233</v>
       </c>
       <c r="H139" s="74" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="I139" s="74"/>
       <c r="J139" s="74"/>
@@ -43627,7 +43623,7 @@
         <v>233</v>
       </c>
       <c r="H140" s="73" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I140" s="73"/>
       <c r="J140" s="73"/>
@@ -44608,10 +44604,10 @@
         <v>338</v>
       </c>
       <c r="H166" s="114" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="I166" s="82" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="J166" s="114" t="s">
         <v>922</v>
@@ -44648,10 +44644,10 @@
         <v>338</v>
       </c>
       <c r="H167" s="115" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="I167" s="74" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="J167" s="115" t="s">
         <v>922</v>
@@ -44688,10 +44684,10 @@
         <v>338</v>
       </c>
       <c r="H168" s="114" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I168" s="82" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="J168" s="114" t="s">
         <v>922</v>
@@ -44728,10 +44724,10 @@
         <v>338</v>
       </c>
       <c r="H169" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I169" s="74" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="J169" s="115" t="s">
         <v>922</v>
@@ -44768,10 +44764,10 @@
         <v>338</v>
       </c>
       <c r="H170" s="114" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I170" s="82" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="J170" s="114" t="s">
         <v>922</v>
@@ -44808,10 +44804,10 @@
         <v>338</v>
       </c>
       <c r="H171" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I171" s="74" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="J171" s="115" t="s">
         <v>922</v>
@@ -44848,10 +44844,10 @@
         <v>338</v>
       </c>
       <c r="H172" s="114" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I172" s="82" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="J172" s="114" t="s">
         <v>922</v>
@@ -44888,10 +44884,10 @@
         <v>338</v>
       </c>
       <c r="H173" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I173" s="74" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="J173" s="115" t="s">
         <v>922</v>
@@ -44928,10 +44924,10 @@
         <v>338</v>
       </c>
       <c r="H174" s="114" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I174" s="82" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="J174" s="114" t="s">
         <v>922</v>
@@ -44968,10 +44964,10 @@
         <v>338</v>
       </c>
       <c r="H175" s="115" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="I175" s="115" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="J175" s="115" t="s">
         <v>922</v>
@@ -45010,7 +45006,7 @@
         <v>965</v>
       </c>
       <c r="I176" s="73" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="J176" s="114" t="s">
         <v>922</v>
@@ -45046,10 +45042,10 @@
         <v>338</v>
       </c>
       <c r="H177" s="115" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="I177" s="74" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="J177" s="115" t="s">
         <v>922</v>
@@ -50033,13 +50029,13 @@
         <v>CLV</v>
       </c>
       <c r="D46" s="82" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E46" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F46" s="82" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G46" s="82" t="s">
         <v>111</v>
@@ -50048,7 +50044,7 @@
         <v>1016</v>
       </c>
       <c r="I46" s="82" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J46" s="82" t="s">
         <v>102</v>
@@ -50058,19 +50054,19 @@
         <v>p-clv-web-lb-fe</v>
       </c>
       <c r="L46" s="82" t="s">
+        <v>1117</v>
+      </c>
+      <c r="M46" s="82" t="s">
         <v>1118</v>
       </c>
-      <c r="M46" s="82" t="s">
-        <v>1119</v>
-      </c>
       <c r="N46" s="82" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="O46" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P46" s="82" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="Q46" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50086,13 +50082,13 @@
         <v>CLV</v>
       </c>
       <c r="D47" s="74" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E47" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F47" s="74" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G47" s="74" t="s">
         <v>111</v>
@@ -50101,7 +50097,7 @@
         <v>1016</v>
       </c>
       <c r="I47" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J47" s="74" t="s">
         <v>102</v>
@@ -50114,16 +50110,16 @@
         <v>317</v>
       </c>
       <c r="M47" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N47" s="74" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="O47" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P47" s="74" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="Q47" s="74" t="str">
         <f t="shared" si="6"/>
@@ -50139,13 +50135,13 @@
         <v>CLV</v>
       </c>
       <c r="D48" s="82" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E48" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F48" s="82" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G48" s="82" t="s">
         <v>111</v>
@@ -50154,7 +50150,7 @@
         <v>1016</v>
       </c>
       <c r="I48" s="82" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J48" s="82" t="s">
         <v>102</v>
@@ -50164,19 +50160,19 @@
         <v>p-clv-ssrap-lb-fe</v>
       </c>
       <c r="L48" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="M48" s="82" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N48" s="82" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="O48" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P48" s="82" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="Q48" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50192,13 +50188,13 @@
         <v>CLV</v>
       </c>
       <c r="D49" s="74" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E49" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F49" s="74" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G49" s="74" t="s">
         <v>111</v>
@@ -50207,7 +50203,7 @@
         <v>1016</v>
       </c>
       <c r="I49" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J49" s="74" t="s">
         <v>102</v>
@@ -50220,16 +50216,16 @@
         <v>317</v>
       </c>
       <c r="M49" s="74" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N49" s="74" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="O49" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P49" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="Q49" s="74" t="str">
         <f t="shared" si="6"/>
@@ -50245,13 +50241,13 @@
         <v>CLV</v>
       </c>
       <c r="D50" s="82" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E50" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F50" s="82" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G50" s="82" t="s">
         <v>111</v>
@@ -50260,7 +50256,7 @@
         <v>1016</v>
       </c>
       <c r="I50" s="82" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J50" s="82" t="s">
         <v>102</v>
@@ -50270,19 +50266,19 @@
         <v>p-clv-admap-lb-fe</v>
       </c>
       <c r="L50" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="M50" s="82" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="N50" s="82" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="O50" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P50" s="82" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="Q50" s="82" t="str">
         <f t="shared" si="6"/>
@@ -50309,7 +50305,7 @@
         <v>1016</v>
       </c>
       <c r="I51" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J51" s="74" t="s">
         <v>102</v>
@@ -50354,7 +50350,7 @@
         <v>1016</v>
       </c>
       <c r="I52" s="82" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J52" s="82" t="s">
         <v>102</v>
@@ -52771,17 +52767,17 @@
         <v>CLV</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-web-lb-pb443</v>
       </c>
       <c r="G73" s="82" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H73" s="82">
         <v>443</v>
@@ -52804,17 +52800,17 @@
         <v>CLV</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="15"/>
         <v>p-dis-clvap-lb-pb8080</v>
       </c>
       <c r="G74" s="74" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H74" s="74">
         <v>8080</v>
@@ -52837,17 +52833,17 @@
         <v>CLV</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-ssrap-lb-pb8080</v>
       </c>
       <c r="G75" s="82" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H75" s="82">
         <v>8080</v>
@@ -52870,17 +52866,17 @@
         <v>CLV</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-admweb-lb-pb443</v>
       </c>
       <c r="G76" s="74" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H76" s="74">
         <v>443</v>
@@ -52903,17 +52899,17 @@
         <v>CLV</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-clv-admap-lb-pb8080</v>
       </c>
       <c r="G77" s="82" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="H77" s="82">
         <v>8080</v>
@@ -53245,6 +53241,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -53388,35 +53399,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -53438,9 +53424,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20261001_리소스배포_운영.xlsx
+++ b/서버정보/20261001_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF02489-BB04-4A3B-BFEE-D81C565C7694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60776426-D69A-4E14-99FE-E5800CDEE1E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8154" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8152" uniqueCount="1166">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -37976,7 +37976,7 @@
         <v>128</v>
       </c>
       <c r="M168" s="80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N168" s="80" t="s">
         <v>191</v>
@@ -50293,9 +50293,7 @@
         <f t="array" ref="C51">UPPER(INDEX(_xlfn.TEXTSPLIT($F51, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D51" s="74" t="s">
-        <v>922</v>
-      </c>
+      <c r="D51" s="74"/>
       <c r="E51" s="74" t="s">
         <v>24</v>
       </c>
@@ -50338,9 +50336,7 @@
         <f t="array" ref="C52">UPPER(INDEX(_xlfn.TEXTSPLIT($F52, "-"), 3))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D52" s="82" t="s">
-        <v>922</v>
-      </c>
+      <c r="D52" s="82"/>
       <c r="E52" s="82" t="s">
         <v>24</v>
       </c>
